--- a/data/trans_dic/P23_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,89; 46,76</t>
+          <t>37,26; 46,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,07; 41,32</t>
+          <t>32,23; 41,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,18; 39,39</t>
+          <t>30,12; 39,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,4; 41,11</t>
+          <t>32,05; 40,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,43; 39,61</t>
+          <t>30,01; 39,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,95; 31,32</t>
+          <t>22,99; 31,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,03; 42,11</t>
+          <t>35,97; 42,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,51; 38,91</t>
+          <t>32,62; 38,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,88; 34,66</t>
+          <t>27,63; 34,37</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,58; 57,85</t>
+          <t>50,68; 58,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,89; 54,57</t>
+          <t>46,84; 54,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,45; 49,7</t>
+          <t>41,7; 50,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,77; 41,5</t>
+          <t>33,6; 41,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,16; 44,61</t>
+          <t>36,86; 44,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,9; 41,8</t>
+          <t>33,82; 41,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,09; 49,62</t>
+          <t>43,77; 49,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,3; 49,05</t>
+          <t>43,2; 48,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,13; 44,79</t>
+          <t>39,14; 44,71</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,65; 57,51</t>
+          <t>49,24; 57,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,94; 51,41</t>
+          <t>44,07; 51,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,33; 44,16</t>
+          <t>36,18; 43,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,85; 41,33</t>
+          <t>33,63; 41,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,55; 38,77</t>
+          <t>31,21; 38,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,07; 37,05</t>
+          <t>29,97; 37,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,34; 47,69</t>
+          <t>42,2; 47,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,73; 43,9</t>
+          <t>38,61; 44,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,21; 39,78</t>
+          <t>34,09; 39,54</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,04; 49,94</t>
+          <t>40,63; 49,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,64; 50,76</t>
+          <t>41,16; 49,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,19; 47,2</t>
+          <t>38,82; 47,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,45; 32,31</t>
+          <t>24,06; 31,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,05; 43,39</t>
+          <t>35,08; 43,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,78; 39,59</t>
+          <t>31,74; 39,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,74; 39,98</t>
+          <t>33,84; 39,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,18; 45,38</t>
+          <t>39,34; 45,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,66; 42,58</t>
+          <t>36,54; 42,15</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28,41; 38,3</t>
+          <t>29,28; 38,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,81; 41,58</t>
+          <t>31,55; 41,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,37; 35,5</t>
+          <t>26,25; 35,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 15,21</t>
+          <t>8,81; 15,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 19,09</t>
+          <t>11,92; 19,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 27,46</t>
+          <t>19,21; 26,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,34; 25,48</t>
+          <t>19,43; 25,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,62; 28,71</t>
+          <t>22,36; 28,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,87; 30,05</t>
+          <t>23,97; 29,69</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,33; 22,79</t>
+          <t>13,99; 22,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,12; 21,62</t>
+          <t>12,66; 22,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 21,7</t>
+          <t>13,13; 22,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,12</t>
+          <t>0,83; 3,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,37</t>
+          <t>3,2; 8,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 11,49</t>
+          <t>5,19; 11,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,82</t>
+          <t>7,56; 11,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 13,35</t>
+          <t>8,14; 13,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,03; 14,94</t>
+          <t>10,14; 15,51</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 15,65</t>
+          <t>7,34; 15,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,06; 15,5</t>
+          <t>7,08; 15,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,16</t>
+          <t>6,75; 13,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,2</t>
+          <t>0,33; 3,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,89</t>
+          <t>0,26; 3,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,07</t>
+          <t>0,69; 4,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,08</t>
+          <t>3,33; 6,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,12</t>
+          <t>3,36; 6,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,76</t>
+          <t>3,51; 6,91</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,46; 44,04</t>
+          <t>40,59; 44,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,86; 41,33</t>
+          <t>37,88; 41,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,41; 36,82</t>
+          <t>33,38; 36,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,11; 27,19</t>
+          <t>24,15; 26,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,88; 28,93</t>
+          <t>25,92; 28,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,68; 27,64</t>
+          <t>24,63; 27,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,61; 34,98</t>
+          <t>32,56; 35,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,16; 34,63</t>
+          <t>32,26; 34,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,29; 31,62</t>
+          <t>29,32; 31,6</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>186812; 230525</t>
+          <t>183681; 228896</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>145629; 187643</t>
+          <t>146372; 187477</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126605; 165208</t>
+          <t>126347; 165473</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>151451; 192196</t>
+          <t>149812; 189078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>130602; 170022</t>
+          <t>128806; 167835</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90812; 123967</t>
+          <t>90995; 124623</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>346097; 404483</t>
+          <t>345469; 405192</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>287151; 343744</t>
+          <t>288172; 344351</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>227263; 282569</t>
+          <t>225211; 280220</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>372038; 425464</t>
+          <t>372735; 426928</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>322158; 374929</t>
+          <t>321799; 376728</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244748; 293458</t>
+          <t>246258; 295575</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>211202; 259601</t>
+          <t>210158; 257342</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>226740; 272211</t>
+          <t>224948; 272853</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>191061; 235565</t>
+          <t>190593; 236277</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>600039; 675295</t>
+          <t>595668; 670585</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>561726; 636282</t>
+          <t>560404; 634612</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>451560; 516842</t>
+          <t>451640; 515961</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>317087; 367317</t>
+          <t>314486; 365658</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>299150; 350009</t>
+          <t>300014; 352230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>242667; 295029</t>
+          <t>241705; 292468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>233501; 285075</t>
+          <t>231949; 287484</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>223987; 275197</t>
+          <t>221537; 276138</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>198589; 244723</t>
+          <t>197920; 245906</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>562393; 633562</t>
+          <t>560629; 631987</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>538582; 610567</t>
+          <t>536913; 612046</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>454501; 528498</t>
+          <t>452934; 525224</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>213044; 259258</t>
+          <t>210904; 258605</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>255941; 311998</t>
+          <t>252975; 306570</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>253205; 304927</t>
+          <t>250782; 304513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126093; 166612</t>
+          <t>124076; 164904</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>215977; 267391</t>
+          <t>216178; 268361</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>205606; 256156</t>
+          <t>205357; 254014</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>349117; 413668</t>
+          <t>350197; 410189</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>482263; 558525</t>
+          <t>484219; 556558</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>474020; 550508</t>
+          <t>472457; 544996</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>109848; 148107</t>
+          <t>113224; 148358</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>136621; 178559</t>
+          <t>135475; 177482</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126011; 169646</t>
+          <t>125451; 168060</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35857; 61454</t>
+          <t>35575; 62900</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52747; 85471</t>
+          <t>53366; 85060</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95907; 136149</t>
+          <t>95243; 133819</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>152935; 201462</t>
+          <t>153621; 201060</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>198465; 251835</t>
+          <t>196115; 254089</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>232382; 292545</t>
+          <t>233352; 289122</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41938; 66669</t>
+          <t>40946; 66732</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>37554; 66987</t>
+          <t>39213; 68496</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45592; 72535</t>
+          <t>43907; 74340</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2826; 14123</t>
+          <t>2833; 13351</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11513; 29630</t>
+          <t>11317; 30472</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20451; 43407</t>
+          <t>19593; 41574</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47755; 75126</t>
+          <t>48053; 76143</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54166; 88616</t>
+          <t>54010; 90789</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71407; 106354</t>
+          <t>72234; 110461</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15017; 32851</t>
+          <t>15410; 32477</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17630; 38738</t>
+          <t>17695; 38070</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17213; 33697</t>
+          <t>17286; 33638</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1130; 10701</t>
+          <t>1115; 11607</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1009; 11236</t>
+          <t>1009; 12889</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2770; 16241</t>
+          <t>2768; 16517</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18368; 38526</t>
+          <t>18099; 37871</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21035; 45472</t>
+          <t>21474; 44440</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22126; 44301</t>
+          <t>23001; 45231</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1325414; 1442511</t>
+          <t>1329366; 1446641</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1296941; 1415781</t>
+          <t>1297780; 1415261</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1133536; 1249039</t>
+          <t>1132509; 1247052</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>814610; 918767</t>
+          <t>815961; 910974</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>920492; 1029014</t>
+          <t>921956; 1029669</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>873361; 978159</t>
+          <t>871670; 977404</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2170312; 2328069</t>
+          <t>2166858; 2330261</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2245409; 2417827</t>
+          <t>2252453; 2413925</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2029989; 2191972</t>
+          <t>2032585; 2190225</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,26; 46,43</t>
+          <t>37,45; 46,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,23; 41,28</t>
+          <t>31,87; 41,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,12; 39,45</t>
+          <t>29,97; 39,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,05; 40,45</t>
+          <t>31,9; 40,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,01; 39,1</t>
+          <t>30,11; 39,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,99; 31,49</t>
+          <t>22,83; 31,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,97; 42,19</t>
+          <t>35,94; 42,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,62; 38,98</t>
+          <t>32,38; 38,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,63; 34,37</t>
+          <t>27,78; 34,33</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,68; 58,05</t>
+          <t>50,16; 57,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,84; 54,83</t>
+          <t>46,93; 54,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,7; 50,06</t>
+          <t>41,38; 49,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,6; 41,14</t>
+          <t>33,04; 41,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,86; 44,71</t>
+          <t>36,89; 44,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,82; 41,93</t>
+          <t>34,25; 42,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,77; 49,27</t>
+          <t>43,5; 49,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,2; 48,92</t>
+          <t>43,04; 48,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,14; 44,71</t>
+          <t>38,97; 44,86</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,24; 57,25</t>
+          <t>48,9; 57,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,07; 51,74</t>
+          <t>43,76; 51,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,18; 43,78</t>
+          <t>36,45; 44,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,63; 41,68</t>
+          <t>33,68; 41,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,21; 38,9</t>
+          <t>31,3; 38,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,97; 37,23</t>
+          <t>29,87; 37,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,2; 47,57</t>
+          <t>42,28; 47,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,61; 44,01</t>
+          <t>38,87; 43,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,09; 39,54</t>
+          <t>34,0; 39,49</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,63; 49,81</t>
+          <t>41,36; 49,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,16; 49,88</t>
+          <t>41,4; 49,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,82; 47,13</t>
+          <t>38,66; 47,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,06; 31,98</t>
+          <t>24,37; 32,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,08; 43,55</t>
+          <t>34,72; 42,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,74; 39,26</t>
+          <t>31,72; 39,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,84; 39,64</t>
+          <t>33,81; 39,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,34; 45,22</t>
+          <t>39,35; 45,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,54; 42,15</t>
+          <t>36,5; 42,11</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,28; 38,36</t>
+          <t>28,48; 37,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,55; 41,33</t>
+          <t>31,85; 41,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,25; 35,17</t>
+          <t>26,19; 35,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 15,57</t>
+          <t>8,38; 15,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 19,0</t>
+          <t>11,88; 19,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,21; 26,99</t>
+          <t>19,06; 26,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,43; 25,43</t>
+          <t>19,46; 25,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,36; 28,96</t>
+          <t>22,42; 28,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23,97; 29,69</t>
+          <t>23,8; 29,92</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,99; 22,81</t>
+          <t>14,17; 22,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,66; 22,11</t>
+          <t>12,44; 21,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,13; 22,24</t>
+          <t>13,22; 21,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,89</t>
+          <t>0,82; 3,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 8,61</t>
+          <t>3,21; 8,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,01</t>
+          <t>5,51; 10,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 11,98</t>
+          <t>7,47; 12,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 13,68</t>
+          <t>8,44; 13,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,14; 15,51</t>
+          <t>10,16; 15,46</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 15,47</t>
+          <t>6,95; 15,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 15,24</t>
+          <t>7,32; 15,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,75; 13,13</t>
+          <t>6,76; 13,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,48</t>
+          <t>0,34; 3,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,31</t>
+          <t>0,26; 3,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,14</t>
+          <t>0,68; 4,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,96</t>
+          <t>3,45; 7,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,96</t>
+          <t>3,22; 7,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,91</t>
+          <t>3,53; 6,87</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,59; 44,17</t>
+          <t>40,64; 44,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,88; 41,31</t>
+          <t>37,85; 41,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,38; 36,76</t>
+          <t>33,65; 36,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24,15; 26,96</t>
+          <t>24,13; 27,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,92; 28,95</t>
+          <t>25,88; 29,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,63; 27,62</t>
+          <t>24,63; 27,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,56; 35,02</t>
+          <t>32,66; 34,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,26; 34,57</t>
+          <t>32,27; 34,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,32; 31,6</t>
+          <t>29,35; 31,64</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>183681; 228896</t>
+          <t>184614; 229863</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>146372; 187477</t>
+          <t>144723; 186619</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126347; 165473</t>
+          <t>125719; 164573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149812; 189078</t>
+          <t>149109; 187624</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>128806; 167835</t>
+          <t>129226; 168384</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90995; 124623</t>
+          <t>90352; 124750</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>345469; 405192</t>
+          <t>345174; 405154</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>288172; 344351</t>
+          <t>286078; 341992</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>225211; 280220</t>
+          <t>226507; 279848</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>372735; 426928</t>
+          <t>368895; 425481</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>321799; 376728</t>
+          <t>322456; 373900</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>246258; 295575</t>
+          <t>244337; 293556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>210158; 257342</t>
+          <t>206673; 260646</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>224948; 272853</t>
+          <t>225119; 273326</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190593; 236277</t>
+          <t>193039; 239245</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>595668; 670585</t>
+          <t>591984; 667771</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>560404; 634612</t>
+          <t>558386; 633092</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>451640; 515961</t>
+          <t>449674; 517690</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>314486; 365658</t>
+          <t>312294; 368691</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>300014; 352230</t>
+          <t>297948; 349009</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>241705; 292468</t>
+          <t>243522; 294247</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>231949; 287484</t>
+          <t>232278; 284485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>221537; 276138</t>
+          <t>222220; 273674</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>197920; 245906</t>
+          <t>197257; 245724</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>560629; 631987</t>
+          <t>561652; 634996</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>536913; 612046</t>
+          <t>540568; 611768</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>452934; 525224</t>
+          <t>451699; 524655</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>210904; 258605</t>
+          <t>214743; 258844</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>252975; 306570</t>
+          <t>254439; 306001</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>250782; 304513</t>
+          <t>249750; 305086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124076; 164904</t>
+          <t>125659; 167436</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>216178; 268361</t>
+          <t>213943; 264395</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>205357; 254014</t>
+          <t>205186; 254108</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>350197; 410189</t>
+          <t>349842; 412491</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>484219; 556558</t>
+          <t>484378; 556061</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>472457; 544996</t>
+          <t>471895; 544464</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>113224; 148358</t>
+          <t>110144; 146628</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>135475; 177482</t>
+          <t>136759; 180272</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125451; 168060</t>
+          <t>125185; 168245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35575; 62900</t>
+          <t>33863; 61300</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>53366; 85060</t>
+          <t>53185; 85499</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95243; 133819</t>
+          <t>94486; 133653</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>153621; 201060</t>
+          <t>153889; 199316</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>196115; 254089</t>
+          <t>196655; 252701</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>233352; 289122</t>
+          <t>231726; 291316</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40946; 66732</t>
+          <t>41452; 65864</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39213; 68496</t>
+          <t>38541; 66479</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43907; 74340</t>
+          <t>44203; 72489</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2833; 13351</t>
+          <t>2819; 13136</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11317; 30472</t>
+          <t>11356; 30601</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19593; 41574</t>
+          <t>20819; 41477</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48053; 76143</t>
+          <t>47497; 76448</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54010; 90789</t>
+          <t>55994; 89249</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72234; 110461</t>
+          <t>72358; 110091</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15410; 32477</t>
+          <t>14578; 31956</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17695; 38070</t>
+          <t>18278; 38607</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17286; 33638</t>
+          <t>17320; 34166</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1115; 11607</t>
+          <t>1129; 11211</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1009; 12889</t>
+          <t>1006; 11906</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2768; 16517</t>
+          <t>2724; 17157</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18099; 37871</t>
+          <t>18739; 39712</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21474; 44440</t>
+          <t>20546; 45497</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23001; 45231</t>
+          <t>23141; 44968</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1329366; 1446641</t>
+          <t>1331274; 1442553</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1297780; 1415261</t>
+          <t>1296778; 1414730</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1132509; 1247052</t>
+          <t>1141425; 1252088</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>815961; 910974</t>
+          <t>815438; 919173</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>921956; 1029669</t>
+          <t>920335; 1033648</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>871670; 977404</t>
+          <t>871656; 984620</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2166858; 2330261</t>
+          <t>2173732; 2325182</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2252453; 2413925</t>
+          <t>2253291; 2411864</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2032585; 2190225</t>
+          <t>2034452; 2193205</t>
         </is>
       </c>
     </row>
